--- a/DTY May26產銷260515-1200+280+30_clear.xlsx
+++ b/DTY May26產銷260515-1200+280+30_clear.xlsx
@@ -6404,16 +6404,18 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr"/>
+          <t>5/22-5/31</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="H89" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>FP82169R</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
@@ -6425,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M89" s="5" t="inlineStr"/>
       <c r="N89" s="5" t="n">
@@ -6440,7 +6442,7 @@
         <v>16</v>
       </c>
       <c r="U89" s="5" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="V89" s="5" t="inlineStr"/>
       <c r="W89" s="5" t="inlineStr"/>
